--- a/Board/bom/micropet_v3.1a-bom.xlsx
+++ b/Board/bom/micropet_v3.1a-bom.xlsx
@@ -526,10 +526,10 @@
     <t xml:space="preserve">VIAPLCC</t>
   </si>
   <si>
-    <t xml:space="preserve">955-W65C22N6TPLG-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W65C22N6TPLG-14</t>
+    <t xml:space="preserve">955-W65C22S6TPLG-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W65C22S6TPLG-14</t>
   </si>
   <si>
     <t xml:space="preserve">PLCC44 Socket</t>
@@ -1100,7 +1100,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1133,17 +1133,14 @@
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1206,7 +1203,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1227,11 +1224,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1267,19 +1260,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1479,12 +1460,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="7.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="19.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19.48"/>
   </cols>
   <sheetData>
-    <row r="1" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1509,11 +1490,11 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5" t="s">
+      <c r="I1" s="3"/>
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="5"/>
+      <c r="K1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -1528,31 +1509,31 @@
       <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1564,10 +1545,10 @@
       <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1587,10 +1568,10 @@
       <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -1610,16 +1591,16 @@
       <c r="E6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1639,10 +1620,10 @@
       <c r="E7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>35</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -1662,10 +1643,10 @@
       <c r="E8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>19</v>
       </c>
       <c r="J8" s="1" t="s">
@@ -1673,7 +1654,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1685,24 +1666,24 @@
       <c r="E9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1711,22 +1692,22 @@
       <c r="C10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="11" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1740,13 +1721,13 @@
       <c r="C11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="11" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1763,10 +1744,10 @@
       <c r="E12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>62</v>
       </c>
       <c r="H12" s="1" t="s">
@@ -1792,10 +1773,10 @@
       <c r="E13" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>70</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -1821,7 +1802,7 @@
       <c r="G14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="J14" s="0" t="s">
+      <c r="J14" s="1" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1844,7 +1825,7 @@
       <c r="G15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="10" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1861,10 +1842,10 @@
       <c r="E16" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>86</v>
       </c>
       <c r="J16" s="1" t="s">
@@ -1884,10 +1865,10 @@
       <c r="E17" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="13" t="s">
         <v>92</v>
       </c>
       <c r="J17" s="1" t="s">
@@ -1907,10 +1888,10 @@
       <c r="E18" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="6" t="s">
         <v>98</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -1930,10 +1911,10 @@
       <c r="E19" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="6" t="s">
         <v>104</v>
       </c>
       <c r="J19" s="1" t="s">
@@ -1953,10 +1934,10 @@
       <c r="E20" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="6" t="s">
         <v>110</v>
       </c>
       <c r="J20" s="1" t="s">
@@ -1979,7 +1960,7 @@
       <c r="F21" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="6" t="s">
         <v>116</v>
       </c>
       <c r="J21" s="1" t="s">
@@ -1999,10 +1980,10 @@
       <c r="F22" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G22" s="12" t="n">
         <v>830207670409</v>
       </c>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="11" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2019,13 +2000,13 @@
       <c r="E23" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="J23" s="17" t="s">
+      <c r="J23" s="6" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2053,20 +2034,20 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -2078,10 +2059,10 @@
       <c r="E26" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="6" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2098,10 +2079,10 @@
       <c r="E27" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="6" t="s">
         <v>141</v>
       </c>
     </row>
@@ -2118,25 +2099,25 @@
       <c r="E28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="6" t="n">
         <v>860010272001</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
@@ -2151,22 +2132,22 @@
       <c r="E30" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="G30" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I30" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="J30" s="7" t="s">
+      <c r="J30" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="K30" s="7" t="s">
+      <c r="K30" s="6" t="s">
         <v>147</v>
       </c>
     </row>
@@ -2183,37 +2164,37 @@
       <c r="E31" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="J31" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="K31" s="7" t="s">
+      <c r="K31" s="6" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
@@ -2274,25 +2255,25 @@
       <c r="E35" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="13" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
@@ -2301,10 +2282,10 @@
       <c r="C37" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="6" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2315,10 +2296,10 @@
       <c r="C38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="6" t="s">
         <v>175</v>
       </c>
     </row>
@@ -2329,10 +2310,10 @@
       <c r="C39" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="G39" s="6" t="s">
         <v>178</v>
       </c>
     </row>
@@ -2343,25 +2324,25 @@
       <c r="C40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G40" s="6" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
@@ -2498,17 +2479,14 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0"/>
-      <c r="B51" s="0"/>
       <c r="C51" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="0"/>
-      <c r="E51" s="0"/>
-      <c r="F51" s="0" t="s">
+      <c r="D51" s="1"/>
+      <c r="F51" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="G51" s="0" t="s">
+      <c r="G51" s="1" t="s">
         <v>205</v>
       </c>
     </row>
@@ -2525,25 +2503,25 @@
       <c r="E52" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="G52" s="7" t="s">
+      <c r="G52" s="6" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="7"/>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7"/>
+      <c r="K53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
@@ -2566,17 +2544,17 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="7"/>
+      <c r="I55" s="7"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
@@ -2591,10 +2569,10 @@
       <c r="E56" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G56" s="7" t="s">
+      <c r="G56" s="6" t="s">
         <v>219</v>
       </c>
     </row>
@@ -2611,25 +2589,25 @@
       <c r="E57" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F57" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G57" s="7" t="s">
+      <c r="G57" s="6" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="7"/>
+      <c r="I58" s="7"/>
+      <c r="J58" s="7"/>
+      <c r="K58" s="7"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
@@ -2644,10 +2622,10 @@
       <c r="E59" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F59" s="18" t="s">
+      <c r="F59" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="G59" s="18" t="s">
+      <c r="G59" s="14" t="s">
         <v>226</v>
       </c>
     </row>
@@ -2664,33 +2642,29 @@
       <c r="E60" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="G60" s="7" t="s">
+      <c r="G60" s="6" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0"/>
-      <c r="B61" s="0"/>
-      <c r="C61" s="0"/>
-      <c r="D61" s="0"/>
-      <c r="E61" s="0"/>
-      <c r="F61" s="0"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
@@ -2702,16 +2676,16 @@
       <c r="C63" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E63" s="19" t="n">
+      <c r="E63" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="G63" s="7" t="s">
+      <c r="G63" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="H63" s="7"/>
+      <c r="H63" s="6"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
@@ -2726,10 +2700,10 @@
       <c r="E64" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F64" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="G64" s="7" t="s">
+      <c r="G64" s="6" t="s">
         <v>239</v>
       </c>
     </row>
@@ -2786,21 +2760,21 @@
       <c r="E67" s="2" t="n">
         <v>390</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="G67" s="7" t="s">
+      <c r="G67" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="H67" s="7" t="s">
+      <c r="H67" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="I67" s="7" t="s">
+      <c r="I67" s="6" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="11" t="s">
         <v>251</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -2812,10 +2786,10 @@
       <c r="E68" s="2" t="n">
         <v>470</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="F68" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="G68" s="7" t="s">
+      <c r="G68" s="6" t="s">
         <v>253</v>
       </c>
     </row>
@@ -2852,10 +2826,10 @@
       <c r="E70" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F70" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G70" s="7" t="s">
+      <c r="G70" s="6" t="s">
         <v>260</v>
       </c>
     </row>
@@ -2892,10 +2866,10 @@
       <c r="E72" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F72" s="18" t="s">
+      <c r="F72" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="G72" s="18" t="s">
+      <c r="G72" s="14" t="s">
         <v>269</v>
       </c>
     </row>
@@ -2920,7 +2894,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="10" t="s">
         <v>274</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -2946,16 +2920,16 @@
       <c r="C75" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E75" s="19" t="s">
+      <c r="E75" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="F75" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="G75" s="7" t="s">
+      <c r="G75" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="H75" s="7"/>
+      <c r="H75" s="6"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
@@ -2970,10 +2944,10 @@
       <c r="E76" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F76" s="7" t="s">
+      <c r="F76" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="G76" s="7" t="s">
+      <c r="G76" s="6" t="s">
         <v>284</v>
       </c>
     </row>
@@ -2990,10 +2964,10 @@
       <c r="E77" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F77" s="7" t="s">
+      <c r="F77" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="G77" s="7" t="s">
+      <c r="G77" s="6" t="s">
         <v>287</v>
       </c>
     </row>
@@ -3010,25 +2984,25 @@
       <c r="E78" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="F78" s="7" t="s">
+      <c r="F78" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="G78" s="7" t="s">
+      <c r="G78" s="6" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="8"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7"/>
+      <c r="J79" s="7"/>
+      <c r="K79" s="7"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
@@ -3043,33 +3017,29 @@
       <c r="E80" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F80" s="18" t="s">
+      <c r="F80" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="G80" s="18" t="s">
+      <c r="G80" s="14" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="8"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8"/>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
+      <c r="H81" s="7"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0"/>
-      <c r="B82" s="0"/>
-      <c r="C82" s="0"/>
-      <c r="D82" s="0"/>
-      <c r="E82" s="0"/>
-      <c r="F82" s="0"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
@@ -3084,10 +3054,10 @@
       <c r="E83" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="F83" s="7" t="s">
+      <c r="F83" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="G83" s="7" t="s">
+      <c r="G83" s="6" t="s">
         <v>299</v>
       </c>
     </row>
@@ -3129,12 +3099,8 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0"/>
-      <c r="B86" s="0"/>
-      <c r="C86" s="0"/>
-      <c r="D86" s="0"/>
-      <c r="E86" s="0"/>
-      <c r="F86" s="0"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
@@ -3149,32 +3115,23 @@
       <c r="E87" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="F87" s="7" t="s">
+      <c r="F87" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="G87" s="7" t="s">
+      <c r="G87" s="6" t="s">
         <v>313</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="I87" s="1"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0"/>
-      <c r="B88" s="0"/>
-      <c r="C88" s="0"/>
-      <c r="D88" s="0"/>
-      <c r="E88" s="0"/>
-      <c r="F88" s="0"/>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0"/>
-      <c r="B89" s="0"/>
-      <c r="C89" s="0"/>
-      <c r="D89" s="0"/>
-      <c r="E89" s="0"/>
-      <c r="F89" s="0"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
@@ -3189,10 +3146,10 @@
       <c r="E90" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="F90" s="7" t="s">
+      <c r="F90" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="G90" s="7" t="s">
+      <c r="G90" s="6" t="s">
         <v>319</v>
       </c>
     </row>
@@ -3243,41 +3200,33 @@
       <c r="C93" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F93" s="18" t="s">
+      <c r="F93" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="G93" s="18" t="s">
+      <c r="G93" s="14" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0"/>
-      <c r="B94" s="0"/>
-      <c r="C94" s="0"/>
-      <c r="D94" s="0"/>
-      <c r="E94" s="0"/>
-      <c r="F94" s="0"/>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0"/>
-      <c r="B95" s="0"/>
-      <c r="C95" s="0"/>
-      <c r="D95" s="0"/>
-      <c r="E95" s="0"/>
-      <c r="F95" s="0"/>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="8"/>
-      <c r="B96" s="8"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
-      <c r="I96" s="8"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="8"/>
+      <c r="A96" s="7"/>
+      <c r="B96" s="7"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7"/>
+      <c r="J96" s="7"/>
+      <c r="K96" s="7"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
@@ -3292,10 +3241,10 @@
       <c r="E97" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="F97" s="7" t="s">
+      <c r="F97" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="G97" s="7" t="s">
+      <c r="G97" s="6" t="s">
         <v>335</v>
       </c>
     </row>
@@ -3335,10 +3284,10 @@
       <c r="E99" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F99" s="7" t="s">
+      <c r="F99" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="G99" s="7" t="s">
+      <c r="G99" s="6" t="s">
         <v>345</v>
       </c>
     </row>
@@ -3388,7 +3337,7 @@
       <c r="F102" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="G102" s="7" t="s">
+      <c r="G102" s="6" t="s">
         <v>356</v>
       </c>
     </row>
